--- a/results/0916-all/川滇高原山地农林牧区/tech_selected_summary.xlsx
+++ b/results/0916-all/川滇高原山地农林牧区/tech_selected_summary.xlsx
@@ -343,220 +343,220 @@
     <t>镇雄县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>技术63</t>
-  </si>
-  <si>
-    <t>技术64</t>
-  </si>
-  <si>
-    <t>技术65</t>
-  </si>
-  <si>
-    <t>技术66</t>
-  </si>
-  <si>
-    <t>技术67</t>
-  </si>
-  <si>
-    <t>技术68</t>
-  </si>
-  <si>
-    <t>技术69</t>
-  </si>
-  <si>
-    <t>技术70</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Tech63</t>
+  </si>
+  <si>
+    <t>Tech64</t>
+  </si>
+  <si>
+    <t>Tech65</t>
+  </si>
+  <si>
+    <t>Tech66</t>
+  </si>
+  <si>
+    <t>Tech67</t>
+  </si>
+  <si>
+    <t>Tech68</t>
+  </si>
+  <si>
+    <t>Tech69</t>
+  </si>
+  <si>
+    <t>Tech70</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -670,7 +670,7 @@
     <t>irrigation (water-saving irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 72157253.19</t>
+    <t>72157253.19</t>
   </si>
   <si>
     <t>Increasing byproduct_beef cattle</t>
@@ -709,10 +709,10 @@
     <t>tillage management (zero tillage)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 153066257.01</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>153066257.01</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>rolller press_beef cattle</t>
@@ -721,10 +721,10 @@
     <t>EEF(CRF)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 33219898.95</t>
-  </si>
-  <si>
-    <t>总经济成本: 22993268.58</t>
+    <t>33219898.95</t>
+  </si>
+  <si>
+    <t>22993268.58</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
@@ -757,16 +757,16 @@
     <t>EEF(CRF)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 53510607.70</t>
-  </si>
-  <si>
-    <t>总经济成本: 12006072.63</t>
-  </si>
-  <si>
-    <t>总经济成本: 12815816.35</t>
-  </si>
-  <si>
-    <t>总经济成本: 26214422.04</t>
+    <t>53510607.70</t>
+  </si>
+  <si>
+    <t>12006072.63</t>
+  </si>
+  <si>
+    <t>12815816.35</t>
+  </si>
+  <si>
+    <t>26214422.04</t>
   </si>
   <si>
     <t>chemical amendments_poultry</t>
@@ -790,25 +790,25 @@
     <t>irrigation (drip irrigation)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 367112892.92</t>
-  </si>
-  <si>
-    <t>总经济成本: 1029084.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 4532183.03</t>
+    <t>367112892.92</t>
+  </si>
+  <si>
+    <t>1029084.20</t>
+  </si>
+  <si>
+    <t>4532183.03</t>
   </si>
   <si>
     <t>Plant-derived N substitution_rice</t>
   </si>
   <si>
-    <t>总经济成本: 16647010.07</t>
-  </si>
-  <si>
-    <t>总经济成本: 27611538.74</t>
-  </si>
-  <si>
-    <t>总经济成本: 1117682.22</t>
+    <t>16647010.07</t>
+  </si>
+  <si>
+    <t>27611538.74</t>
+  </si>
+  <si>
+    <t>1117682.22</t>
   </si>
   <si>
     <t>Probiotics_poultry</t>
@@ -841,7 +841,7 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 160232322.32</t>
+    <t>160232322.32</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -850,16 +850,16 @@
     <t>surface crust cover_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 115482152.99</t>
-  </si>
-  <si>
-    <t>总经济成本: 397711.62</t>
-  </si>
-  <si>
-    <t>总经济成本: 133842682.30</t>
-  </si>
-  <si>
-    <t>总经济成本: 1735018.13</t>
+    <t>115482152.99</t>
+  </si>
+  <si>
+    <t>397711.62</t>
+  </si>
+  <si>
+    <t>133842682.30</t>
+  </si>
+  <si>
+    <t>1735018.13</t>
   </si>
   <si>
     <t>Increasing concentrate level (grain)_beef cattle</t>
@@ -883,7 +883,7 @@
     <t>biochar_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 562754332.00</t>
+    <t>562754332.00</t>
   </si>
   <si>
     <t>Feedstock adjustment_beef cattle</t>
@@ -901,10 +901,10 @@
     <t>cover crop (mix)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 89664578.12</t>
-  </si>
-  <si>
-    <t>总经济成本: 96379512.07</t>
+    <t>89664578.12</t>
+  </si>
+  <si>
+    <t>96379512.07</t>
   </si>
   <si>
     <t>Yucca extract_Poultry</t>
@@ -940,7 +940,7 @@
     <t>tillage management (zero tillage)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 711312986.84</t>
+    <t>711312986.84</t>
   </si>
   <si>
     <t>Decreasing grass maturity_sheep &amp; goat</t>
@@ -955,79 +955,79 @@
     <t>biochar_pig</t>
   </si>
   <si>
-    <t>总经济成本: 320985939.23</t>
-  </si>
-  <si>
-    <t>总经济成本: 4265539.03</t>
-  </si>
-  <si>
-    <t>总经济成本: 121734214.72</t>
-  </si>
-  <si>
-    <t>总经济成本: 3020790.44</t>
-  </si>
-  <si>
-    <t>总经济成本: 57663064.62</t>
-  </si>
-  <si>
-    <t>总经济成本: 91484306.63</t>
-  </si>
-  <si>
-    <t>总经济成本: 166343912.71</t>
-  </si>
-  <si>
-    <t>总经济成本: 2110202.17</t>
+    <t>320985939.23</t>
+  </si>
+  <si>
+    <t>4265539.03</t>
+  </si>
+  <si>
+    <t>121734214.72</t>
+  </si>
+  <si>
+    <t>3020790.44</t>
+  </si>
+  <si>
+    <t>57663064.62</t>
+  </si>
+  <si>
+    <t>91484306.63</t>
+  </si>
+  <si>
+    <t>166343912.71</t>
+  </si>
+  <si>
+    <t>2110202.17</t>
   </si>
   <si>
     <t>Frequent removal_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 252033556.57</t>
-  </si>
-  <si>
-    <t>总经济成本: 130358145.79</t>
-  </si>
-  <si>
-    <t>总经济成本: 215011671.75</t>
-  </si>
-  <si>
-    <t>总经济成本: 23630617.70</t>
-  </si>
-  <si>
-    <t>总经济成本: 1071238.09</t>
-  </si>
-  <si>
-    <t>总经济成本: 2606417.98</t>
-  </si>
-  <si>
-    <t>总经济成本: 84486538.19</t>
-  </si>
-  <si>
-    <t>总经济成本: 579158.78</t>
-  </si>
-  <si>
-    <t>总经济成本: 276827104.67</t>
-  </si>
-  <si>
-    <t>总经济成本: 15845085.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 108071917.46</t>
-  </si>
-  <si>
-    <t>总经济成本: 118820123.36</t>
-  </si>
-  <si>
-    <t>总经济成本: 195715244.91</t>
-  </si>
-  <si>
-    <t>总经济成本: 11133269.77</t>
-  </si>
-  <si>
-    <t>总经济成本: 37433825.97</t>
-  </si>
-  <si>
-    <t>总经济成本: 109257062.63</t>
+    <t>252033556.57</t>
+  </si>
+  <si>
+    <t>130358145.79</t>
+  </si>
+  <si>
+    <t>215011671.75</t>
+  </si>
+  <si>
+    <t>23630617.70</t>
+  </si>
+  <si>
+    <t>1071238.09</t>
+  </si>
+  <si>
+    <t>2606417.98</t>
+  </si>
+  <si>
+    <t>84486538.19</t>
+  </si>
+  <si>
+    <t>579158.78</t>
+  </si>
+  <si>
+    <t>276827104.67</t>
+  </si>
+  <si>
+    <t>15845085.00</t>
+  </si>
+  <si>
+    <t>108071917.46</t>
+  </si>
+  <si>
+    <t>118820123.36</t>
+  </si>
+  <si>
+    <t>195715244.91</t>
+  </si>
+  <si>
+    <t>11133269.77</t>
+  </si>
+  <si>
+    <t>37433825.97</t>
+  </si>
+  <si>
+    <t>109257062.63</t>
   </si>
   <si>
     <t>Chemical amendments_pig</t>
@@ -1039,13 +1039,13 @@
     <t>cover crop (mix)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 300237939.28</t>
-  </si>
-  <si>
-    <t>总经济成本: 50523662.18</t>
-  </si>
-  <si>
-    <t>总经济成本: 12128592.05</t>
+    <t>300237939.28</t>
+  </si>
+  <si>
+    <t>50523662.18</t>
+  </si>
+  <si>
+    <t>12128592.05</t>
   </si>
   <si>
     <t>Adsorbent_poultry</t>
@@ -1057,22 +1057,22 @@
     <t>biochar_maize</t>
   </si>
   <si>
-    <t>总经济成本: 142701543.68</t>
-  </si>
-  <si>
-    <t>总经济成本: 3616519.23</t>
-  </si>
-  <si>
-    <t>总经济成本: 185927737.67</t>
-  </si>
-  <si>
-    <t>总经济成本: 78803276.80</t>
-  </si>
-  <si>
-    <t>总经济成本: 12613115.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 70936078.41</t>
+    <t>142701543.68</t>
+  </si>
+  <si>
+    <t>3616519.23</t>
+  </si>
+  <si>
+    <t>185927737.67</t>
+  </si>
+  <si>
+    <t>78803276.80</t>
+  </si>
+  <si>
+    <t>12613115.00</t>
+  </si>
+  <si>
+    <t>70936078.41</t>
   </si>
   <si>
     <t>Plant-derived N substitution_maize</t>
@@ -1084,43 +1084,43 @@
     <t>irrigation (water-saving irrigation)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 1188087764.56</t>
-  </si>
-  <si>
-    <t>总经济成本: 34116782.15</t>
-  </si>
-  <si>
-    <t>总经济成本: 21400.62</t>
-  </si>
-  <si>
-    <t>总经济成本: 48077154.90</t>
-  </si>
-  <si>
-    <t>总经济成本: 25583591.08</t>
-  </si>
-  <si>
-    <t>总经济成本: 127178375.01</t>
-  </si>
-  <si>
-    <t>总经济成本: 3478213.09</t>
-  </si>
-  <si>
-    <t>总经济成本: 21242438.67</t>
-  </si>
-  <si>
-    <t>总经济成本: 802203.22</t>
-  </si>
-  <si>
-    <t>总经济成本: 131750305.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 972189.52</t>
-  </si>
-  <si>
-    <t>总经济成本: 22863607.60</t>
-  </si>
-  <si>
-    <t>总经济成本: 496630503.45</t>
+    <t>1188087764.56</t>
+  </si>
+  <si>
+    <t>34116782.15</t>
+  </si>
+  <si>
+    <t>21400.62</t>
+  </si>
+  <si>
+    <t>48077154.90</t>
+  </si>
+  <si>
+    <t>25583591.08</t>
+  </si>
+  <si>
+    <t>127178375.01</t>
+  </si>
+  <si>
+    <t>3478213.09</t>
+  </si>
+  <si>
+    <t>21242438.67</t>
+  </si>
+  <si>
+    <t>802203.22</t>
+  </si>
+  <si>
+    <t>131750305.20</t>
+  </si>
+  <si>
+    <t>972189.52</t>
+  </si>
+  <si>
+    <t>22863607.60</t>
+  </si>
+  <si>
+    <t>496630503.45</t>
   </si>
 </sst>
 </file>
